--- a/04_Information_Classification/Information_Classification_Register.xlsx
+++ b/04_Information_Classification/Information_Classification_Register.xlsx
@@ -402,8 +402,8 @@
       <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
+          <fgColor rgb="FF156082"/>
+          <bgColor rgb="FF156082"/>
         </patternFill>
       </fill>
       <border/>
@@ -422,8 +422,8 @@
       <font/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
       <border/>
@@ -431,16 +431,16 @@
     <dxf>
       <border>
         <left style="thin">
-          <color theme="4"/>
+          <color rgb="FF156082"/>
         </left>
         <right style="thin">
-          <color theme="4"/>
+          <color rgb="FF156082"/>
         </right>
         <top style="thin">
-          <color theme="4"/>
+          <color rgb="FF156082"/>
         </top>
         <bottom style="thin">
-          <color theme="4"/>
+          <color rgb="FF156082"/>
         </bottom>
         <vertical style="thin">
           <color rgb="FFD4D4D4"/>
@@ -1140,911 +1140,186 @@
         <v>46259.0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="C20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="C21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="C22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="C23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="C24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="C25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="C26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="C27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="C28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="C29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="C30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="C31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="C32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="C33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="C34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="C35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="C36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="C37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="I37" s="2"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="C38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="I38" s="2"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="C39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="I39" s="2"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="C40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="C41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="C42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="C43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="C44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="C45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="C46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="C47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="I47" s="2"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="C48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="I48" s="2"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="C49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="I49" s="2"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="C50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="I50" s="2"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="C51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="I51" s="2"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="C52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="I52" s="2"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="C53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="I53" s="2"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="C54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="I54" s="2"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="C55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="I55" s="2"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="C56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="I56" s="2"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="C57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="I57" s="2"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="C58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="I58" s="2"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="C59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="I59" s="2"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="C60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="I60" s="2"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="C61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="I61" s="2"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="C62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="I62" s="2"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="C63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="I63" s="2"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="C64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="I64" s="2"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="C65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="I65" s="2"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="C66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="I66" s="2"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="C67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="I67" s="2"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="C68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="I68" s="2"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="C69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="I69" s="2"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="C70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="I70" s="2"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="C71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="I71" s="2"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="C72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="I72" s="2"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="C73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="I73" s="2"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="C74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="I74" s="2"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="C75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="I75" s="2"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="C76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="I76" s="2"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="C77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="I77" s="2"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="C78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="I78" s="2"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="C79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="I79" s="2"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="C80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="I80" s="2"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="C81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="I81" s="2"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="C82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="I82" s="2"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="C83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="I83" s="2"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="C84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="I84" s="2"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="C85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="I85" s="2"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="C86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="I86" s="2"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="C87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="I87" s="2"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="C88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="I88" s="2"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="C89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="I89" s="2"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="C90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="I90" s="2"/>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="C91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="I91" s="2"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="C92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="I92" s="2"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="C93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="I93" s="2"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="C94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="I94" s="2"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="C95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="I95" s="2"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="C96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="I96" s="2"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="C97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="I97" s="2"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="C98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="I98" s="2"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="C99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="I99" s="2"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="C100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="I100" s="2"/>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="C101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="I101" s="2"/>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="C102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="I102" s="2"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="C103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="I103" s="2"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="C104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="I104" s="2"/>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="C105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="I105" s="2"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1">
-      <c r="C106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="I106" s="2"/>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="C107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="I107" s="2"/>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="C108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="I108" s="2"/>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="C109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="I109" s="2"/>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="C110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="I110" s="2"/>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="C111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="I111" s="2"/>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="C112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="I112" s="2"/>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="C113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="I113" s="2"/>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="C114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="I114" s="2"/>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="C115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="I115" s="2"/>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="C116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="I116" s="2"/>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="C117" s="2"/>
-      <c r="E117" s="2"/>
-      <c r="I117" s="2"/>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="C118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="I118" s="2"/>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="C119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="I119" s="2"/>
-    </row>
-    <row r="120" ht="15.75" customHeight="1">
-      <c r="C120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="I120" s="2"/>
-    </row>
-    <row r="121" ht="15.75" customHeight="1">
-      <c r="C121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="I121" s="2"/>
-    </row>
-    <row r="122" ht="15.75" customHeight="1">
-      <c r="C122" s="2"/>
-      <c r="E122" s="2"/>
-      <c r="I122" s="2"/>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="C123" s="2"/>
-      <c r="E123" s="2"/>
-      <c r="I123" s="2"/>
-    </row>
-    <row r="124" ht="15.75" customHeight="1">
-      <c r="C124" s="2"/>
-      <c r="E124" s="2"/>
-      <c r="I124" s="2"/>
-    </row>
-    <row r="125" ht="15.75" customHeight="1">
-      <c r="C125" s="2"/>
-      <c r="E125" s="2"/>
-      <c r="I125" s="2"/>
-    </row>
-    <row r="126" ht="15.75" customHeight="1">
-      <c r="C126" s="2"/>
-      <c r="E126" s="2"/>
-      <c r="I126" s="2"/>
-    </row>
-    <row r="127" ht="15.75" customHeight="1">
-      <c r="C127" s="2"/>
-      <c r="E127" s="2"/>
-      <c r="I127" s="2"/>
-    </row>
-    <row r="128" ht="15.75" customHeight="1">
-      <c r="C128" s="2"/>
-      <c r="E128" s="2"/>
-      <c r="I128" s="2"/>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
-      <c r="C129" s="2"/>
-      <c r="E129" s="2"/>
-      <c r="I129" s="2"/>
-    </row>
-    <row r="130" ht="15.75" customHeight="1">
-      <c r="C130" s="2"/>
-      <c r="E130" s="2"/>
-      <c r="I130" s="2"/>
-    </row>
-    <row r="131" ht="15.75" customHeight="1">
-      <c r="C131" s="2"/>
-      <c r="E131" s="2"/>
-      <c r="I131" s="2"/>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="C132" s="2"/>
-      <c r="E132" s="2"/>
-      <c r="I132" s="2"/>
-    </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="C133" s="2"/>
-      <c r="E133" s="2"/>
-      <c r="I133" s="2"/>
-    </row>
-    <row r="134" ht="15.75" customHeight="1">
-      <c r="C134" s="2"/>
-      <c r="E134" s="2"/>
-      <c r="I134" s="2"/>
-    </row>
-    <row r="135" ht="15.75" customHeight="1">
-      <c r="C135" s="2"/>
-      <c r="E135" s="2"/>
-      <c r="I135" s="2"/>
-    </row>
-    <row r="136" ht="15.75" customHeight="1">
-      <c r="C136" s="2"/>
-      <c r="E136" s="2"/>
-      <c r="I136" s="2"/>
-    </row>
-    <row r="137" ht="15.75" customHeight="1">
-      <c r="C137" s="2"/>
-      <c r="E137" s="2"/>
-      <c r="I137" s="2"/>
-    </row>
-    <row r="138" ht="15.75" customHeight="1">
-      <c r="C138" s="2"/>
-      <c r="E138" s="2"/>
-      <c r="I138" s="2"/>
-    </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="C139" s="2"/>
-      <c r="E139" s="2"/>
-      <c r="I139" s="2"/>
-    </row>
-    <row r="140" ht="15.75" customHeight="1">
-      <c r="C140" s="2"/>
-      <c r="E140" s="2"/>
-      <c r="I140" s="2"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1">
-      <c r="C141" s="2"/>
-      <c r="E141" s="2"/>
-      <c r="I141" s="2"/>
-    </row>
-    <row r="142" ht="15.75" customHeight="1">
-      <c r="C142" s="2"/>
-      <c r="E142" s="2"/>
-      <c r="I142" s="2"/>
-    </row>
-    <row r="143" ht="15.75" customHeight="1">
-      <c r="C143" s="2"/>
-      <c r="E143" s="2"/>
-      <c r="I143" s="2"/>
-    </row>
-    <row r="144" ht="15.75" customHeight="1">
-      <c r="C144" s="2"/>
-      <c r="E144" s="2"/>
-      <c r="I144" s="2"/>
-    </row>
-    <row r="145" ht="15.75" customHeight="1">
-      <c r="C145" s="2"/>
-      <c r="E145" s="2"/>
-      <c r="I145" s="2"/>
-    </row>
-    <row r="146" ht="15.75" customHeight="1">
-      <c r="C146" s="2"/>
-      <c r="E146" s="2"/>
-      <c r="I146" s="2"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1">
-      <c r="C147" s="2"/>
-      <c r="E147" s="2"/>
-      <c r="I147" s="2"/>
-    </row>
-    <row r="148" ht="15.75" customHeight="1">
-      <c r="C148" s="2"/>
-      <c r="E148" s="2"/>
-      <c r="I148" s="2"/>
-    </row>
-    <row r="149" ht="15.75" customHeight="1">
-      <c r="C149" s="2"/>
-      <c r="E149" s="2"/>
-      <c r="I149" s="2"/>
-    </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="C150" s="2"/>
-      <c r="E150" s="2"/>
-      <c r="I150" s="2"/>
-    </row>
-    <row r="151" ht="15.75" customHeight="1">
-      <c r="C151" s="2"/>
-      <c r="E151" s="2"/>
-      <c r="I151" s="2"/>
-    </row>
-    <row r="152" ht="15.75" customHeight="1">
-      <c r="C152" s="2"/>
-      <c r="E152" s="2"/>
-      <c r="I152" s="2"/>
-    </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="C153" s="2"/>
-      <c r="E153" s="2"/>
-      <c r="I153" s="2"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1">
-      <c r="C154" s="2"/>
-      <c r="E154" s="2"/>
-      <c r="I154" s="2"/>
-    </row>
-    <row r="155" ht="15.75" customHeight="1">
-      <c r="C155" s="2"/>
-      <c r="E155" s="2"/>
-      <c r="I155" s="2"/>
-    </row>
-    <row r="156" ht="15.75" customHeight="1">
-      <c r="C156" s="2"/>
-      <c r="E156" s="2"/>
-      <c r="I156" s="2"/>
-    </row>
-    <row r="157" ht="15.75" customHeight="1">
-      <c r="C157" s="2"/>
-      <c r="E157" s="2"/>
-      <c r="I157" s="2"/>
-    </row>
-    <row r="158" ht="15.75" customHeight="1">
-      <c r="C158" s="2"/>
-      <c r="E158" s="2"/>
-      <c r="I158" s="2"/>
-    </row>
-    <row r="159" ht="15.75" customHeight="1">
-      <c r="C159" s="2"/>
-      <c r="E159" s="2"/>
-      <c r="I159" s="2"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="C160" s="2"/>
-      <c r="E160" s="2"/>
-      <c r="I160" s="2"/>
-    </row>
-    <row r="161" ht="15.75" customHeight="1">
-      <c r="C161" s="2"/>
-      <c r="E161" s="2"/>
-      <c r="I161" s="2"/>
-    </row>
-    <row r="162" ht="15.75" customHeight="1">
-      <c r="C162" s="2"/>
-      <c r="E162" s="2"/>
-      <c r="I162" s="2"/>
-    </row>
-    <row r="163" ht="15.75" customHeight="1">
-      <c r="C163" s="2"/>
-      <c r="E163" s="2"/>
-      <c r="I163" s="2"/>
-    </row>
-    <row r="164" ht="15.75" customHeight="1">
-      <c r="C164" s="2"/>
-      <c r="E164" s="2"/>
-      <c r="I164" s="2"/>
-    </row>
-    <row r="165" ht="15.75" customHeight="1">
-      <c r="C165" s="2"/>
-      <c r="E165" s="2"/>
-      <c r="I165" s="2"/>
-    </row>
-    <row r="166" ht="15.75" customHeight="1">
-      <c r="C166" s="2"/>
-      <c r="E166" s="2"/>
-      <c r="I166" s="2"/>
-    </row>
-    <row r="167" ht="15.75" customHeight="1">
-      <c r="C167" s="2"/>
-      <c r="E167" s="2"/>
-      <c r="I167" s="2"/>
-    </row>
-    <row r="168" ht="15.75" customHeight="1">
-      <c r="C168" s="2"/>
-      <c r="E168" s="2"/>
-      <c r="I168" s="2"/>
-    </row>
-    <row r="169" ht="15.75" customHeight="1">
-      <c r="C169" s="2"/>
-      <c r="E169" s="2"/>
-      <c r="I169" s="2"/>
-    </row>
-    <row r="170" ht="15.75" customHeight="1">
-      <c r="C170" s="2"/>
-      <c r="E170" s="2"/>
-      <c r="I170" s="2"/>
-    </row>
-    <row r="171" ht="15.75" customHeight="1">
-      <c r="C171" s="2"/>
-      <c r="E171" s="2"/>
-      <c r="I171" s="2"/>
-    </row>
-    <row r="172" ht="15.75" customHeight="1">
-      <c r="C172" s="2"/>
-      <c r="E172" s="2"/>
-      <c r="I172" s="2"/>
-    </row>
-    <row r="173" ht="15.75" customHeight="1">
-      <c r="C173" s="2"/>
-      <c r="E173" s="2"/>
-      <c r="I173" s="2"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1">
-      <c r="C174" s="2"/>
-      <c r="E174" s="2"/>
-      <c r="I174" s="2"/>
-    </row>
-    <row r="175" ht="15.75" customHeight="1">
-      <c r="C175" s="2"/>
-      <c r="E175" s="2"/>
-      <c r="I175" s="2"/>
-    </row>
-    <row r="176" ht="15.75" customHeight="1">
-      <c r="C176" s="2"/>
-      <c r="E176" s="2"/>
-      <c r="I176" s="2"/>
-    </row>
-    <row r="177" ht="15.75" customHeight="1">
-      <c r="C177" s="2"/>
-      <c r="E177" s="2"/>
-      <c r="I177" s="2"/>
-    </row>
-    <row r="178" ht="15.75" customHeight="1">
-      <c r="C178" s="2"/>
-      <c r="E178" s="2"/>
-      <c r="I178" s="2"/>
-    </row>
-    <row r="179" ht="15.75" customHeight="1">
-      <c r="C179" s="2"/>
-      <c r="E179" s="2"/>
-      <c r="I179" s="2"/>
-    </row>
-    <row r="180" ht="15.75" customHeight="1">
-      <c r="C180" s="2"/>
-      <c r="E180" s="2"/>
-      <c r="I180" s="2"/>
-    </row>
-    <row r="181" ht="15.75" customHeight="1">
-      <c r="C181" s="2"/>
-      <c r="E181" s="2"/>
-      <c r="I181" s="2"/>
-    </row>
-    <row r="182" ht="15.75" customHeight="1">
-      <c r="C182" s="2"/>
-      <c r="E182" s="2"/>
-      <c r="I182" s="2"/>
-    </row>
-    <row r="183" ht="15.75" customHeight="1">
-      <c r="C183" s="2"/>
-      <c r="E183" s="2"/>
-      <c r="I183" s="2"/>
-    </row>
-    <row r="184" ht="15.75" customHeight="1">
-      <c r="C184" s="2"/>
-      <c r="E184" s="2"/>
-      <c r="I184" s="2"/>
-    </row>
-    <row r="185" ht="15.75" customHeight="1">
-      <c r="C185" s="2"/>
-      <c r="E185" s="2"/>
-      <c r="I185" s="2"/>
-    </row>
-    <row r="186" ht="15.75" customHeight="1">
-      <c r="C186" s="2"/>
-      <c r="E186" s="2"/>
-      <c r="I186" s="2"/>
-    </row>
-    <row r="187" ht="15.75" customHeight="1">
-      <c r="C187" s="2"/>
-      <c r="E187" s="2"/>
-      <c r="I187" s="2"/>
-    </row>
-    <row r="188" ht="15.75" customHeight="1">
-      <c r="C188" s="2"/>
-      <c r="E188" s="2"/>
-      <c r="I188" s="2"/>
-    </row>
-    <row r="189" ht="15.75" customHeight="1">
-      <c r="C189" s="2"/>
-      <c r="E189" s="2"/>
-      <c r="I189" s="2"/>
-    </row>
-    <row r="190" ht="15.75" customHeight="1">
-      <c r="C190" s="2"/>
-      <c r="E190" s="2"/>
-      <c r="I190" s="2"/>
-    </row>
-    <row r="191" ht="15.75" customHeight="1">
-      <c r="C191" s="2"/>
-      <c r="E191" s="2"/>
-      <c r="I191" s="2"/>
-    </row>
-    <row r="192" ht="15.75" customHeight="1">
-      <c r="C192" s="2"/>
-      <c r="E192" s="2"/>
-      <c r="I192" s="2"/>
-    </row>
-    <row r="193" ht="15.75" customHeight="1">
-      <c r="C193" s="2"/>
-      <c r="E193" s="2"/>
-      <c r="I193" s="2"/>
-    </row>
-    <row r="194" ht="15.75" customHeight="1">
-      <c r="C194" s="2"/>
-      <c r="E194" s="2"/>
-      <c r="I194" s="2"/>
-    </row>
-    <row r="195" ht="15.75" customHeight="1">
-      <c r="C195" s="2"/>
-      <c r="E195" s="2"/>
-      <c r="I195" s="2"/>
-    </row>
-    <row r="196" ht="15.75" customHeight="1">
-      <c r="C196" s="2"/>
-      <c r="E196" s="2"/>
-      <c r="I196" s="2"/>
-    </row>
-    <row r="197" ht="15.75" customHeight="1">
-      <c r="C197" s="2"/>
-      <c r="E197" s="2"/>
-      <c r="I197" s="2"/>
-    </row>
-    <row r="198" ht="15.75" customHeight="1">
-      <c r="C198" s="2"/>
-      <c r="E198" s="2"/>
-      <c r="I198" s="2"/>
-    </row>
-    <row r="199" ht="15.75" customHeight="1">
-      <c r="C199" s="2"/>
-      <c r="E199" s="2"/>
-      <c r="I199" s="2"/>
-    </row>
-    <row r="200" ht="15.75" customHeight="1">
-      <c r="C200" s="2"/>
-      <c r="E200" s="2"/>
-      <c r="I200" s="2"/>
-    </row>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
     <row r="201" ht="15.75" customHeight="1"/>
     <row r="202" ht="15.75" customHeight="1"/>
     <row r="203" ht="15.75" customHeight="1"/>
@@ -2871,13 +2146,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="C10:C200">
+    <dataValidation type="list" allowBlank="1" sqref="C10:C19">
       <formula1>Lists!$C$2:$C$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E10:E200">
+    <dataValidation type="list" allowBlank="1" sqref="E10:E19">
       <formula1>Lists!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I10:I200">
+    <dataValidation type="list" allowBlank="1" sqref="I10:I19">
       <formula1>Lists!$E$2:$E$5</formula1>
     </dataValidation>
   </dataValidations>
